--- a/output/full_scan/batch_seq0_2026-10-05.xlsx
+++ b/output/full_scan/batch_seq0_2026-10-05.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1157.421637414321</v>
+        <v>1327.421637414321</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>570</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>65.19551465575216</v>
+        <v>65.19551463212666</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>25.75145716769314</v>
+        <v>25.75145712977902</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.196681696357679</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2.249550038399919</v>
+        <v>2.249550040514052</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8111</v>
+        <v>8070</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>936.9716798871688</v>
+        <v>1169.905640632586</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>94.3</v>
+        <v>51.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>73.39954564496263</v>
+        <v>60.59746032660522</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>34.83629737863205</v>
+        <v>15.21024549753422</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.636561398977253</v>
+        <v>2.89910059342623</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.182414538992101</v>
+        <v>0.1422906173434391</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8070</v>
+        <v>8111</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>869.9056406325876</v>
+        <v>1136.971679887169</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>51.7</v>
+        <v>94.3</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>60.59746044034241</v>
+        <v>73.39954555385876</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15.21024531528928</v>
+        <v>34.83629732697025</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.89910059342623</v>
+        <v>2.636561398977253</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,11 +676,11 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1422906173545633</v>
+        <v>1.182414540004675</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>839</v>
+        <v>1039</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>57.2</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>79.56289802343306</v>
+        <v>79.56289801594818</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>27.55518644495543</v>
+        <v>27.5551864578088</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>8.432686174930275</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.612172632711036</v>
+        <v>1.612172632722174</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8086</v>
+        <v>8046</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>769</v>
+        <v>1021.449685310208</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>129</v>
+        <v>1495</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>70.329469257252</v>
+        <v>73.48871012591047</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18.26048075280645</v>
+        <v>22.46952152962865</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5.536139634834691</v>
+        <v>1.288636379633652</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2.213207020713034</v>
+        <v>43.53721633457344</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8081</v>
+        <v>8261</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>768.0450532390236</v>
+        <v>994.7176993941572</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.67622236859077</v>
+        <v>66.02780685002944</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>14.44873176276008</v>
+        <v>13.71073090175966</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.887608620204386</v>
+        <v>4.571769939415715</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.29928919144924</v>
+        <v>3.806158415310747</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8091</v>
+        <v>8081</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>751.3357012542147</v>
+        <v>973.0450532390234</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>69.83888478190948</v>
+        <v>56.67622230834112</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>17.15674418030313</v>
+        <v>14.4487318066823</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4.800735947947523</v>
+        <v>1.887608620204386</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>3.448130751730867</v>
+        <v>1.29928919233944</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8383</v>
+        <v>8086</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>712.3582957526182</v>
+        <v>969</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>69.3</v>
+        <v>129</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.02713446690768</v>
+        <v>70.32946916041328</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14.59747972452121</v>
+        <v>18.26048078635571</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.276791831027992</v>
+        <v>5.536139634834691</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4960199592958487</v>
+        <v>2.213207020935581</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8261</v>
+        <v>8091</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>709.7176993941572</v>
+        <v>921.3357012542126</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>66.02780686333629</v>
+        <v>69.83888473943719</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>13.71073099936854</v>
+        <v>17.15674422652188</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4.571769939415715</v>
+        <v>4.800735947947523</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>3.806158414776632</v>
+        <v>3.44813075228723</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8040</v>
+        <v>8150</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>678.3671440439593</v>
+        <v>921.1895218471616</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>63.85289247986948</v>
+        <v>71.39396792704862</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>30.05063657379208</v>
+        <v>34.09180346130211</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.578489254889743</v>
+        <v>1.961098493794108</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1.244996179845079</v>
+        <v>3.282025862332151</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8215</v>
+        <v>8074</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>663.61585273944</v>
+        <v>804</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>28.6</v>
+        <v>57.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>58.03972121125398</v>
+        <v>64.87406061507134</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>39.08232114294137</v>
+        <v>18.3886927520882</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.7833368047382276</v>
+        <v>6.922224819439239</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.2036827252082587</v>
+        <v>0.8765779965770838</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8050</v>
+        <v>8182</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>657.2709378011619</v>
+        <v>749.8018499691565</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>62</v>
+        <v>44.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>58.48680718439311</v>
+        <v>65.5531735225143</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>26.55621665577803</v>
+        <v>22.07424439805179</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.7163800483644456</v>
+        <v>3.189614543757545</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.5167895912615182</v>
+        <v>0.8047964499493087</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8150</v>
+        <v>8147</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>646.1895218471617</v>
+        <v>724.9839634404859</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>124</v>
+        <v>141.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>71.3939679618516</v>
+        <v>55.17181124244623</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>34.0918034590524</v>
+        <v>31.1606510135562</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.961098493794108</v>
+        <v>1.171052607607617</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>3.282025862276507</v>
+        <v>0.802993291525417</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8074</v>
+        <v>8240</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>634</v>
+        <v>724.7524875580807</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>57.3</v>
+        <v>58</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>64.87406066872281</v>
+        <v>66.49156862590658</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>18.38869274687826</v>
+        <v>39.60163032346584</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>6.922224819439239</v>
+        <v>0.7752487558080671</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.8765779959428364</v>
+        <v>0.6960646912943598</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8299</v>
+        <v>8201</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>624.2582113320537</v>
+        <v>718.7323907636699</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2100</v>
+        <v>16.35</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>51.44178268997074</v>
+        <v>72.92887065740706</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>14.19413783064178</v>
+        <v>54.19486069706258</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7391667867181247</v>
+        <v>2.47323907636699</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.243366392546129</v>
+        <v>0.5682463782707181</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8046</v>
+        <v>8383</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>616.3643529414705</v>
+        <v>712.3582957526182</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1495</v>
+        <v>69.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>73.48871012681683</v>
+        <v>56.02713447882671</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>22.46952152164057</v>
+        <v>14.59747971207433</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.281701933174361</v>
+        <v>1.276791831027992</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>43.53721633546344</v>
+        <v>0.4960199593514801</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8147</v>
+        <v>8038</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>609.9839634404858</v>
+        <v>711.3501762063103</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>141.5</v>
+        <v>35.4</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>55.1718112619909</v>
+        <v>66.17063647317727</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>31.16065100181663</v>
+        <v>28.47481902545888</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.171052607607617</v>
+        <v>1.556099958908777</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.8029932910803304</v>
+        <v>0.4604303857640517</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>9912</v>
+        <v>8042</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>605.9370945158051</v>
+        <v>691.8169828252554</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>13.1</v>
+        <v>118.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>54.21733436009941</v>
+        <v>55.06239579566572</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>32.37540252597631</v>
+        <v>21.72929931763472</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.097753487963498</v>
+        <v>1.220320511713882</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.0075346227165696</v>
+        <v>1.033207211860148</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8064</v>
+        <v>8040</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>602.2123766659904</v>
+        <v>678.3671440439593</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>136.5</v>
+        <v>94</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>58.37344370963134</v>
+        <v>63.85289247821101</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>24.15252001447799</v>
+        <v>30.05063658049444</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5868281411535489</v>
+        <v>0.578489254889743</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.7240685015234591</v>
+        <v>1.244996180000859</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8171</v>
+        <v>8215</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>584.9172785040354</v>
+        <v>663.61585273944</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>20.7</v>
+        <v>28.6</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>60.21278835549697</v>
+        <v>58.03972123386741</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>21.07576633455604</v>
+        <v>39.08232112617869</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.118136852720249</v>
+        <v>0.7833368047382276</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0662088632672283</v>
+        <v>0.203682725275018</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8155</v>
+        <v>8039</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>584.5939374601157</v>
+        <v>661.5901788417874</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>329.5</v>
+        <v>303.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>50.34151265959603</v>
+        <v>58.56203708579351</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>14.04123337377928</v>
+        <v>18.51114847895533</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.320728516651428</v>
+        <v>2.207927288540867</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-1.167143019557819</v>
+        <v>1.691019234375426</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8182</v>
+        <v>8438</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>579.8018499691565</v>
+        <v>659.7355824783164</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>44.8</v>
+        <v>81</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>65.55317349938423</v>
+        <v>66.44044928694167</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>22.0742441074742</v>
+        <v>29.70648849262656</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>3.189614543757545</v>
+        <v>1.91607691592189</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.8047964501607252</v>
+        <v>1.360750319998901</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8042</v>
+        <v>8050</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>576.8169828252554</v>
+        <v>657.2709378011619</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>118.5</v>
+        <v>62</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>55.06239580420672</v>
+        <v>58.48680715933289</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>21.72929935688327</v>
+        <v>26.55621667981488</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.220320511713882</v>
+        <v>0.7163800483644456</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.033207211804519</v>
+        <v>0.5167895913282869</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8210</v>
+        <v>8109</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>570.1121657930304</v>
+        <v>648.0632703669218</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>890</v>
+        <v>139</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>44.98488278648666</v>
+        <v>58.16639984421176</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>21.88550964653183</v>
+        <v>30.10435923683762</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>3.191337651125915</v>
+        <v>1.740099602638811</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>2.801028080173069</v>
+        <v>1.337594058718817</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, williams_r_recovery</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8240</v>
+        <v>8210</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>554.7524875580807</v>
+        <v>645.1121657930303</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>58</v>
+        <v>890</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>66.49156871929111</v>
+        <v>44.98488269331549</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>39.60163027016834</v>
+        <v>21.88550965931152</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7752487558080671</v>
+        <v>3.191337651125915</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.6960646907936376</v>
+        <v>2.801028083511241</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, dealer_buy_3d, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8038</v>
+        <v>8299</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>541.3501762063105</v>
+        <v>624.2582113320537</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>35.4</v>
+        <v>2100</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>66.17063626832238</v>
+        <v>51.44178265204071</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>28.47481897695796</v>
+        <v>14.19413778274381</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.556099958908777</v>
+        <v>0.7391667867181247</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.460430385741798</v>
+        <v>1.243366397441672</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8110</v>
+        <v>9912</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>538.6375745683978</v>
+        <v>605.9370945158051</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>49.2</v>
+        <v>13.1</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>58.21905149701724</v>
+        <v>54.21733450506517</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25.69897290318655</v>
+        <v>32.37540254884261</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7833707255915269</v>
+        <v>1.097753487963498</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.4409270920897008</v>
+        <v>-0.0075346227276969</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8431</v>
+        <v>8064</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>533.6712659223938</v>
+        <v>602.2123766659905</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>63.6</v>
+        <v>136.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>56.00906440427612</v>
+        <v>58.3734437149172</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>34.10266127071608</v>
+        <v>24.15252005228777</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.3121234604922156</v>
+        <v>0.5868281411535489</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.4105373989187115</v>
+        <v>0.724068501645851</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8109</v>
+        <v>8121</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>533.0632703669216</v>
+        <v>600.945329897453</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>139</v>
+        <v>32.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>58.1663998387816</v>
+        <v>61.92176230789299</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>30.1043592398471</v>
+        <v>30.31434529998895</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.740099602638811</v>
+        <v>1.95728576041626</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>1.337594058652034</v>
+        <v>0.840361284409242</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8054</v>
+        <v>8085</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>532.4431043385918</v>
+        <v>588.4827858800824</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>87.3</v>
+        <v>14.85</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.66513883336402</v>
+        <v>61.3821603159416</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>22.5747960810011</v>
+        <v>17.36859369813122</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.072124349264585</v>
+        <v>1.302103697734099</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.7329438961902002</v>
+        <v>-0.0566927866108125</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8213</v>
+        <v>8499</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>531.9579314642654</v>
+        <v>586.167493261426</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>33.85</v>
+        <v>256</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>57.00284223546045</v>
+        <v>51.38091016167744</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>20.57586490097313</v>
+        <v>9.153041597333685</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.7945062098136791</v>
+        <v>1.721832957727242</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1296405747871027</v>
+        <v>3.91822695195383</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8438</v>
+        <v>8171</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>519.7355824783164</v>
+        <v>584.9172785040355</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>81</v>
+        <v>20.7</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>66.44044928353415</v>
+        <v>60.21278823237726</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>29.70648854400184</v>
+        <v>21.0757664016438</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.91607691592189</v>
+        <v>1.118136852720249</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1.360750319976642</v>
+        <v>0.0662088633006091</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8201</v>
+        <v>8155</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>518.7323907636699</v>
+        <v>584.5939374601157</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>16.35</v>
+        <v>329.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>72.92887066352031</v>
+        <v>50.34151255633288</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>54.19486062865005</v>
+        <v>14.04123319535755</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>2.47323907636699</v>
+        <v>1.320728516651428</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.5682463782039597</v>
+        <v>-1.167143017332364</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8443</v>
+        <v>8045</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>503.5948646646336</v>
+        <v>574.8697923781948</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>11.15</v>
+        <v>55.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>44.61126927777778</v>
+        <v>59.60470732078137</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>52.82669130229857</v>
+        <v>22.79240919168434</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.1099656584008322</v>
+        <v>1.031282637887303</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0056440261447103</v>
+        <v>0.5501479724954066</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8162</v>
+        <v>8213</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>498.5439253537483</v>
+        <v>551.9579314642654</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>33.85</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>62.96579841967535</v>
+        <v>57.00284210469572</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>21.99781822146537</v>
+        <v>20.57586501937787</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.222139437512715</v>
+        <v>0.7945062098136791</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.7286408173082186</v>
+        <v>0.1296405752321944</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8926</v>
+        <v>8072</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>498.1091738599233</v>
+        <v>551.104003043221</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>59.1</v>
+        <v>27.1</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>52.54622990945951</v>
+        <v>50.53893552664741</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>12.60314741721451</v>
+        <v>38.94983440800704</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.7159202067429664</v>
+        <v>0.7896460028199138</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1785731330697535</v>
+        <v>0.0528709145248176</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8103</v>
+        <v>8110</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>495.6455681687946</v>
+        <v>538.6375745683978</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>121.5</v>
+        <v>49.2</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>56.02042553771158</v>
+        <v>58.21905149107083</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>36.90751074519385</v>
+        <v>25.69897289851504</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.7268937265045278</v>
+        <v>0.7833707255915269</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-1.318131907906856</v>
+        <v>0.4409270921342071</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8089</v>
+        <v>8431</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>478.3383221877343</v>
+        <v>533.6712659223938</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>19.35</v>
+        <v>63.6</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.3645428779838</v>
+        <v>56.00906427951212</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>27.66842037879947</v>
+        <v>34.1026612161101</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.8923958923079971</v>
+        <v>0.3121234604922156</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1160077914089139</v>
+        <v>-0.4105373981620714</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8499</v>
+        <v>8054</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>476.1674932614262</v>
+        <v>532.4431043385933</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>256</v>
+        <v>87.3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>51.38091024640572</v>
+        <v>55.66513868427909</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>9.153041499327545</v>
+        <v>22.57479605519758</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.721832957727242</v>
+        <v>1.072124349264585</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>3.918226949394596</v>
+        <v>0.7329438969690992</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8085</v>
+        <v>8926</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>473.4827858800823</v>
+        <v>518.1091738599232</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>14.85</v>
+        <v>59.1</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>61.38216039395711</v>
+        <v>52.54622987523651</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>17.36859365177614</v>
+        <v>12.60314741721451</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.302103697734099</v>
+        <v>0.7159202067429664</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.0566927866887021</v>
+        <v>0.1785731330808821</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8039</v>
+        <v>8043</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>461.5901788417873</v>
+        <v>515.1049854061321</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>303.5</v>
+        <v>140.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>58.5620370806886</v>
+        <v>54.14596511907529</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.51114847097478</v>
+        <v>11.67446738229691</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.207927288540867</v>
+        <v>1.12667168857826</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.69101923443111</v>
+        <v>1.255661599518525</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8121</v>
+        <v>8103</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>460.945329897453</v>
+        <v>510.6455681687946</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>32.5</v>
+        <v>121.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>61.92176233143645</v>
+        <v>56.02042548805098</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>30.31434526031171</v>
+        <v>36.90751071872428</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.95728576041626</v>
+        <v>0.7268937265045278</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.8403612844426244</v>
+        <v>-1.318131907678033</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8045</v>
+        <v>8443</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>459.869792378195</v>
+        <v>503.5948646646336</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>55.5</v>
+        <v>11.15</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>59.60470728523232</v>
+        <v>44.61126945686054</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.79240925031024</v>
+        <v>52.82669130229856</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.031282637887303</v>
+        <v>0.1099656584008322</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.5501479729404869</v>
+        <v>-0.0056440261558369</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8277</v>
+        <v>8162</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>456.5277713423041</v>
+        <v>498.5439253537483</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>15.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>78.72872042520171</v>
+        <v>62.96579831655992</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>35.31890429788192</v>
+        <v>21.9978181461979</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5149583455856771</v>
+        <v>1.222139437512715</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.4224195436344624</v>
+        <v>0.7286408176642893</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8131</v>
+        <v>8476</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>449.5514997825924</v>
+        <v>482.6171349741096</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>63.5</v>
+        <v>20.2</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>56.36259779347528</v>
+        <v>55.68969043761619</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10.51109591072282</v>
+        <v>14.41481376114455</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.9185947556832836</v>
+        <v>1.241678222654966</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.480214592344759</v>
+        <v>0.109960824185807</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8072</v>
+        <v>8089</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>441.1040030432206</v>
+        <v>478.3383221877341</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>27.1</v>
+        <v>19.35</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>50.5389356500807</v>
+        <v>58.36454220944776</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>38.94983437290966</v>
+        <v>27.66842046351781</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7896460028199138</v>
+        <v>0.8923958923079971</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0528709144135453</v>
+        <v>0.1160077923213389</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8097</v>
+        <v>8047</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>427.4524164641134</v>
+        <v>468.6301704362958</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>48.85</v>
+        <v>51</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>46.27928983158663</v>
+        <v>53.20995666096333</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>20.99091796958901</v>
+        <v>10.39149658028324</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7280238646248293</v>
+        <v>1.265122673558698</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.1309176986015819</v>
+        <v>1.897249796566522</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8071</v>
+        <v>8277</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>426.6432356245986</v>
+        <v>456.5277713423042</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>22</v>
+        <v>15.3</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>44.64613345560689</v>
+        <v>78.72872041255383</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>11.88586136234005</v>
+        <v>35.3189043519141</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.651511784452786</v>
+        <v>0.5149583455856771</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.114184346492657</v>
+        <v>0.4224195436306484</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8455</v>
+        <v>8131</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>424.4096454361478</v>
+        <v>449.551499782587</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>22.1</v>
+        <v>63.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>51.20389867218933</v>
+        <v>56.36259779347528</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>9.999644710437847</v>
+        <v>10.51109589693155</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.732073299088709</v>
+        <v>0.9185947556832836</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.4930297347206771</v>
+        <v>0.48021459240039</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8068</v>
+        <v>8093</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>411.2166384690254</v>
+        <v>441.4359254281286</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>17.5</v>
+        <v>24.85</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>54.56055643121455</v>
+        <v>51.6164507123755</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>28.64232179911264</v>
+        <v>12.65992371217836</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5409656665603576</v>
+        <v>1.949096543395539</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.1583879261997696</v>
+        <v>0.0597839967292934</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8112</v>
+        <v>8097</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>400.6571015877082</v>
+        <v>427.4524164641134</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>84.09999999999999</v>
+        <v>48.85</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>43.45778711532412</v>
+        <v>46.27928947716722</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.91874971633786</v>
+        <v>20.9909179466556</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9416043188802152</v>
+        <v>0.7280238646248293</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,48 +3220,48 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.2231068362392612</v>
+        <v>0.1309176986015819</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8183</v>
+        <v>8071</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>395.8634049635201</v>
+        <v>426.6432356245986</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>28.2</v>
+        <v>22</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G53" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>44.90268852167593</v>
+        <v>44.64613345560689</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19.14537617696747</v>
+        <v>11.88586137390214</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.870816255095116</v>
+        <v>1.651511784452786</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0686206104713073</v>
+        <v>0.1141843465037861</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8411</v>
+        <v>8455</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>395.1450485636813</v>
+        <v>424.4096454361487</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>11.7</v>
+        <v>22.1</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>25.95829343273464</v>
+        <v>51.2038986867062</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>30.70413781444367</v>
+        <v>9.99964473525152</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.210631300635685</v>
+        <v>2.732073299088709</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.09890421944481061</v>
+        <v>-0.4930297345315166</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8488</v>
+        <v>8068</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>387.9895168330712</v>
+        <v>411.2166384690257</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>9.84</v>
+        <v>17.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>47.01174450169562</v>
+        <v>54.56055629133197</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>36.78909734596181</v>
+        <v>28.64232188172873</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9947408314643206</v>
+        <v>0.5409656665603576</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0239817552394315</v>
+        <v>0.1583879262554079</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8049</v>
+        <v>8442</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>384.0055423402645</v>
+        <v>402.6428903718146</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>24.55</v>
+        <v>45.95</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>45.34253722730149</v>
+        <v>53.52134338802564</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>16.63696748222488</v>
+        <v>10.87985557549009</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.58794181682311</v>
+        <v>0.6801668525973711</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0726685351309517</v>
+        <v>-0.0301038356427862</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8105</v>
+        <v>8112</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>380.4577032112632</v>
+        <v>400.6571015877082</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>15.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>48.90361175369956</v>
+        <v>43.45778711532412</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>21.59499967634187</v>
+        <v>20.91874971206692</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.473815196442934</v>
+        <v>0.9416043188802152</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,48 +3485,48 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1701851116063831</v>
+        <v>0.2231068361613699</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8101</v>
+        <v>8183</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>377.2165370215429</v>
+        <v>395.86340496352</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>11.2</v>
+        <v>28.2</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G58" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>47.59086651882726</v>
+        <v>44.90268850906808</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>12.28166200700535</v>
+        <v>19.1453762418109</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>4.216937772271292</v>
+        <v>1.870816255095116</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.08748288932556129</v>
+        <v>0.0686206105475891</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8043</v>
+        <v>8411</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>375.1049854061321</v>
+        <v>395.1450485636813</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>140.5</v>
+        <v>11.7</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>54.14596509992202</v>
+        <v>25.95829349555957</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>11.67446735967086</v>
+        <v>30.70413784331168</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.12667168857826</v>
+        <v>1.210631300635685</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,11 +3591,11 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>1.255661599485154</v>
+        <v>-0.0989042194670663</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>373.4356242216525</v>
+        <v>393.4356242216525</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>179</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>41.52866588072995</v>
+        <v>41.52866573889143</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>24.77659866252589</v>
+        <v>24.77659875805425</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.3859490464179831</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.068958713988777</v>
+        <v>1.068958714656396</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8476</v>
+        <v>8464</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>367.6171349741096</v>
+        <v>392.4180451484986</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>20.2</v>
+        <v>362.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,49 +3679,49 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>55.68969057439845</v>
+        <v>42.57025855151306</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>14.41481354959229</v>
+        <v>12.1758952666885</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.241678222654966</v>
+        <v>0.3218886438906733</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M61" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1099608240411547</v>
+        <v>-1.393532524123812</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8473</v>
+        <v>8940</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>366.6447208679617</v>
+        <v>389.7400724964836</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>40.35</v>
+        <v>14.95</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>48.06915377744791</v>
+        <v>46.49050002557951</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>25.56518946553858</v>
+        <v>9.537587733757499</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.042569740516471</v>
+        <v>0.3916060706634885</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.2519456035022309</v>
+        <v>0.034649442280078</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8087</v>
+        <v>8096</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>364.2435598074717</v>
+        <v>389.1336703509585</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>50.57764641625247</v>
+        <v>40.21663337197104</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>5.389251708719941</v>
+        <v>33.64765526256736</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>6.72248478160949</v>
+        <v>0.8077851777575658</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.2093523892303626</v>
+        <v>1.305902349763321</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8047</v>
+        <v>8488</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>353.6301704362957</v>
+        <v>387.9895168330712</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>51</v>
+        <v>9.84</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>53.20995666096333</v>
+        <v>47.01173969707254</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>10.39149658079819</v>
+        <v>36.78909516114786</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.265122673558698</v>
+        <v>0.9947408314643206</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>1.897249796588784</v>
+        <v>-0.0239817526579376</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8477</v>
+        <v>8473</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>350.4735228836502</v>
+        <v>386.6447208679617</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>14</v>
+        <v>40.35</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>34.06096358945619</v>
+        <v>48.06915366268096</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.51069445649019</v>
+        <v>25.56518948461448</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.239050399898439</v>
+        <v>1.042569740516471</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0868511337255191</v>
+        <v>0.2519456036913876</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8069</v>
+        <v>8049</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>349.2010232743605</v>
+        <v>384.0055423402647</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>146.5</v>
+        <v>24.55</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>42.95828382580617</v>
+        <v>45.34253710999159</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>31.79903487202495</v>
+        <v>16.63696753087535</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.366008644276648</v>
+        <v>1.58794181682311</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>1.089312378963787</v>
+        <v>0.0726685351086994</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8234</v>
+        <v>8105</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>340.7734078444248</v>
+        <v>380.4577032112632</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>62.8</v>
+        <v>15.3</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45.24525853341881</v>
+        <v>48.90361170075093</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.16707819418283</v>
+        <v>21.59499965589994</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.8600080826612302</v>
+        <v>1.473815196442934</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.1898034620571929</v>
+        <v>0.1701851116770111</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8059</v>
+        <v>8101</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>335.9937307400087</v>
+        <v>377.2165370215431</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>17.8</v>
+        <v>11.2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>61.85467188932741</v>
+        <v>47.59086662087373</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>26.67953433207346</v>
+        <v>12.28166204462802</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.4601632027887078</v>
+        <v>4.216937772271292</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.3148621990502739</v>
+        <v>-0.0874828894813405</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8076</v>
+        <v>8087</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>324.2010293014592</v>
+        <v>364.2435598074718</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>21.4</v>
+        <v>24</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>40.56925998904264</v>
+        <v>50.57764641176647</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>21.82972520584464</v>
+        <v>5.389251711590971</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.744282344978104</v>
+        <v>6.72248478160949</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0779857496848383</v>
+        <v>0.2093523892637491</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8466</v>
+        <v>8462</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>321.1624725377346</v>
+        <v>361.9114174578367</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>15.15</v>
+        <v>157.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.1493294739598</v>
+        <v>39.19727627105161</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>30.01091896682896</v>
+        <v>29.23285384226367</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.1175052302727247</v>
+        <v>0.4293765421527025</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.1004897739977745</v>
+        <v>-0.2830665039831026</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8102</v>
+        <v>8477</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>320.7298244031506</v>
+        <v>350.4735228836502</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>59.6</v>
+        <v>14</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.79025165328976</v>
+        <v>34.06096358945619</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>6.125235462747804</v>
+        <v>23.51069445280165</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4830020434701839</v>
+        <v>1.239050399898439</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.7549507151733188</v>
+        <v>-0.0868511337032644</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8163</v>
+        <v>8069</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>320.1976450567955</v>
+        <v>349.2010232743605</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>30.7</v>
+        <v>146.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>50.79039682695647</v>
+        <v>42.95828347258313</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13.90943281033709</v>
+        <v>31.79903494603482</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.284869057571753</v>
+        <v>1.366008644276648</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.2003142416466279</v>
+        <v>1.089312381300508</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8104</v>
+        <v>8088</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>317.8768152678596</v>
+        <v>348.8288098358946</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>31.35</v>
+        <v>44</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>52.68168554714841</v>
+        <v>51.1652303013899</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>18.4279566576737</v>
+        <v>13.24347275983626</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.005580874448718</v>
+        <v>1.125909416716284</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.2278984182749683</v>
+        <v>0.44628298055188</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8080</v>
+        <v>8234</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>315.2578063120296</v>
+        <v>340.7734078444248</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>28</v>
+        <v>62.8</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.43364295617659</v>
+        <v>45.24525937041913</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>38.94557880748262</v>
+        <v>19.16707815678897</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.436549851839842</v>
+        <v>0.8600080826612302</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-1.138891339754629</v>
+        <v>0.1898034617233863</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8482</v>
+        <v>8104</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>314.9791995227914</v>
+        <v>337.8768152678653</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>48.35</v>
+        <v>31.35</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>51.27114275250273</v>
+        <v>52.68168477661044</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>4.592693470587221</v>
+        <v>18.4279566576737</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.183692975039518</v>
+        <v>1.005580874448718</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0269152100304062</v>
+        <v>0.2278984185308953</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8367</v>
+        <v>8059</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>312.8825254357786</v>
+        <v>335.9937307400087</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>40.75</v>
+        <v>17.8</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>52.20616267965426</v>
+        <v>61.8546717747547</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.57873015633157</v>
+        <v>26.67953463691645</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6710024423039982</v>
+        <v>0.4601632027887078</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0072224917355701</v>
+        <v>0.3148621990312037</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8048</v>
+        <v>9136</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>307.0187790784209</v>
+        <v>330.9953436833901</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>51.3</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>54.62000512141913</v>
+        <v>35.44641727986948</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12.50974851207065</v>
+        <v>18.61500603002524</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.047731151145594</v>
+        <v>0.4849226065069728</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.3816710982557515</v>
+        <v>0.0356446638987268</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8440</v>
+        <v>8076</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>305.3006193529961</v>
+        <v>324.2010293014591</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>20.2</v>
+        <v>21.4</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>50.28751466594649</v>
+        <v>40.56926013252936</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.05262406258167</v>
+        <v>21.82972497918107</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3685039540560875</v>
+        <v>1.744282344978104</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0262329442261807</v>
+        <v>0.0779857496848383</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8390</v>
+        <v>8466</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>304.7963587437397</v>
+        <v>321.1624725377346</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>89</v>
+        <v>15.15</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>33.26850080022167</v>
+        <v>49.14932944116305</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>21.80592668869141</v>
+        <v>30.01091910884644</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2.094401673002585</v>
+        <v>0.1175052302727247</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.042201499793435</v>
+        <v>0.1004897739977745</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8093</v>
+        <v>8102</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>301.4359254281285</v>
+        <v>320.7298244031506</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>24.85</v>
+        <v>59.6</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>51.61645072426679</v>
+        <v>50.79025162899642</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>12.65992362117497</v>
+        <v>6.125235464506063</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.949096543395539</v>
+        <v>0.4830020434701839</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0597839966530123</v>
+        <v>0.7549507151510624</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8442</v>
+        <v>8163</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>292.6428903718146</v>
+        <v>320.1976450567956</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>45.95</v>
+        <v>30.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>53.52134343469207</v>
+        <v>50.79039675864468</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>10.87985557549009</v>
+        <v>13.90943282058178</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6801668525973711</v>
+        <v>1.284869057571753</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0301038355760224</v>
+        <v>0.2003142416800094</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8932</v>
+        <v>8080</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>288.3692509375033</v>
+        <v>315.2578063120296</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>28</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>43.836309258834</v>
+        <v>51.43364294387613</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>18.47695546037029</v>
+        <v>38.94557870483575</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.8722158755791343</v>
+        <v>1.436549851839842</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.4790359141251854</v>
+        <v>-1.138891339587722</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8462</v>
+        <v>8482</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>286.9114174578366</v>
+        <v>314.9791995227914</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>157.5</v>
+        <v>48.35</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>39.19727628541516</v>
+        <v>51.27114270696855</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>29.23285377203269</v>
+        <v>4.592693459911959</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4293765421527025</v>
+        <v>1.183692975039518</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.2830665039831026</v>
+        <v>0.0269152102306937</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8454</v>
+        <v>8367</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>286.5016316229314</v>
+        <v>312.8825254357786</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>234.5</v>
+        <v>40.75</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>39.51081524695054</v>
+        <v>52.20616272192324</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>11.71108612895333</v>
+        <v>16.57873016371006</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.419167105344203</v>
+        <v>0.6710024423039982</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0925125587701849</v>
+        <v>0.0072224917578303</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8463</v>
+        <v>8048</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>284.6524378459167</v>
+        <v>307.0187790784217</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>21</v>
+        <v>51.3</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>43.80844816429757</v>
+        <v>54.62000519898977</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>24.27854148969402</v>
+        <v>12.50974844126613</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>3.48437771975631</v>
+        <v>1.047731151145594</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0119750119904065</v>
+        <v>0.3816710982891407</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8410</v>
+        <v>8440</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>280.6507596404918</v>
+        <v>305.3006193529963</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>27.65</v>
+        <v>20.2</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>27.43113758542792</v>
+        <v>50.28751452335589</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>44.9727498320034</v>
+        <v>18.05262404355125</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.006765301451592</v>
+        <v>0.3685039540560875</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.068731857352666</v>
+        <v>0.0262329442818176</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8940</v>
+        <v>8390</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>279.7400724964836</v>
+        <v>304.7963587437397</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>14.95</v>
+        <v>89</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>46.49049995105842</v>
+        <v>33.2685008373635</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>9.537587662589178</v>
+        <v>21.80592669603714</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3916060706634885</v>
+        <v>2.094401673002585</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0346494423134581</v>
+        <v>-0.0422014999492141</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8464</v>
+        <v>9110</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>277.4180451484985</v>
+        <v>299.7420615804067</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>362.5</v>
+        <v>2.95</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>42.57025834832504</v>
+        <v>52.07788679628055</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.17589534598249</v>
+        <v>4.944468694862584</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3218886438906733</v>
+        <v>0.8393358466351167</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-1.393532524680188</v>
+        <v>0.0879232974401301</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>9105</v>
+        <v>8932</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>271.2515875947341</v>
+        <v>288.3692509375033</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>8.32</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>44.57493782298743</v>
+        <v>43.83630943438967</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>16.5840651726738</v>
+        <v>18.47695549594104</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.9419413999002108</v>
+        <v>0.8722158755791343</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0127949681318016</v>
+        <v>0.4790359167949738</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8271</v>
+        <v>8454</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>255.2942730891117</v>
+        <v>286.5016316229314</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>200.5</v>
+        <v>234.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>39.69477469076472</v>
+        <v>39.51081531504172</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.35718241803727</v>
+        <v>11.71108627547076</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.8555276834628402</v>
+        <v>1.419167105344203</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0559529074318909</v>
+        <v>-0.092512558658897</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5244,21 +5244,21 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8249</v>
+        <v>8463</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>253.1520772141891</v>
+        <v>284.6524378459168</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>40.5</v>
+        <v>21</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>54.05707939416788</v>
+        <v>43.80844809728691</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>19.21650557290485</v>
+        <v>24.27854150229925</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.542136135089733</v>
+        <v>3.48437771975631</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.3473448440127566</v>
+        <v>-0.0119750119681492</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8096</v>
+        <v>8410</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>249.1336703509587</v>
+        <v>280.6507596404918</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>90</v>
+        <v>27.65</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>40.21663334917574</v>
+        <v>27.43113721280688</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>33.64765534167703</v>
+        <v>44.97275003846372</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.8077851777575658</v>
+        <v>1.006765301451592</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>1.305902349518526</v>
+        <v>-0.068731857208012</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>9930</v>
+        <v>9105</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>246.7548417415276</v>
+        <v>271.2515875947337</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>59.4</v>
+        <v>8.32</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>21.34173699441613</v>
+        <v>44.5749378423731</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>29.93740077817981</v>
+        <v>16.58406520180911</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.9047561819321605</v>
+        <v>0.9419413999002108</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1135607834816816</v>
+        <v>-0.0127949681407037</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8176</v>
+        <v>8374</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>246.572306786715</v>
+        <v>261.6962883824956</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>9.76</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>44.77421885890232</v>
+        <v>44.73506071214229</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>25.24935084221599</v>
+        <v>8.478540173441406</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5840655425398537</v>
+        <v>0.8427600546756675</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0022643909819288</v>
+        <v>0.1260681535778751</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8472</v>
+        <v>8271</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>244.0967121365751</v>
+        <v>255.2942730891114</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>66.3</v>
+        <v>200.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>35.48354205719694</v>
+        <v>39.69477459261341</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.65087261070915</v>
+        <v>13.35718233153136</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.3096712136575145</v>
+        <v>0.8555276834628402</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-1.536528743656993</v>
+        <v>-0.0559529066084687</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8423</v>
+        <v>8249</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>239.0622918319388</v>
+        <v>253.152077214189</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>17.8</v>
+        <v>40.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>44.50762753267016</v>
+        <v>54.0570800196812</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>18.87437659640698</v>
+        <v>19.2165055551406</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.793672779005045</v>
+        <v>1.542136135089733</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0142807831986276</v>
+        <v>0.3473448437234477</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8088</v>
+        <v>9930</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>233.8288098358969</v>
+        <v>246.7548417415276</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>44</v>
+        <v>59.4</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>51.16523029327722</v>
+        <v>21.34173715088646</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13.2434727293945</v>
+        <v>29.93740070210241</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.125909416716284</v>
+        <v>0.9047561819321605</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.4462829806742798</v>
+        <v>-0.1135607839045104</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8341</v>
+        <v>8176</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>233.612489681473</v>
+        <v>246.572306786715</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>73.8</v>
+        <v>9.76</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>35.06579085614375</v>
+        <v>44.77421909527119</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.3160100007349</v>
+        <v>25.24935086034438</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.935619530304559</v>
+        <v>0.5840655425398537</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0115360889122193</v>
+        <v>-0.0022643910041823</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8487</v>
+        <v>8472</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>233.1216172571914</v>
+        <v>244.0967121365751</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>70</v>
+        <v>66.3</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>41.8353443245081</v>
+        <v>35.48354208657062</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>12.452460774854</v>
+        <v>28.65087288507457</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>2.696000912150941</v>
+        <v>0.3096712136575145</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0380465097840858</v>
+        <v>-1.536528741943411</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8422</v>
+        <v>8341</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>232.8777828825412</v>
+        <v>233.612489681473</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>25.3</v>
+        <v>73.8</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>38.67093363484749</v>
+        <v>35.06579101057926</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>8.699766222210789</v>
+        <v>15.31600998561445</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.28602224589845</v>
+        <v>1.935619530304559</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0486821926338834</v>
+        <v>-0.0115360889789685</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8481</v>
+        <v>8487</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>231.9877355613575</v>
+        <v>233.1216172571914</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>40.65</v>
+        <v>70</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.03140895497427</v>
+        <v>41.8353443245081</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>9.676647976574344</v>
+        <v>12.4524608527112</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.078911455406599</v>
+        <v>2.696000912150941</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0545757306500209</v>
+        <v>0.0380465098063387</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8404</v>
+        <v>8422</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>226.8391203454094</v>
+        <v>232.8777828825416</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>13</v>
+        <v>25.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>22.53396535148657</v>
+        <v>38.67093472276473</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>50.51727887607487</v>
+        <v>8.699766325318121</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.488946724116117</v>
+        <v>1.28602224589845</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.016447658909596</v>
+        <v>-0.0486821933966815</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>9136</v>
+        <v>8481</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>220.9953436833901</v>
+        <v>231.9877355613575</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>40.65</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>35.44641728714493</v>
+        <v>45.0314090011696</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.61500603148311</v>
+        <v>9.676648031012194</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4849226065069728</v>
+        <v>1.078911455406599</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0356446638965015</v>
+        <v>-0.0545757306611451</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8467</v>
+        <v>8404</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>219.268740454676</v>
+        <v>226.8391203454094</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>88.3</v>
+        <v>13</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>43.85373871646166</v>
+        <v>22.53396553440226</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>8.16482732822284</v>
+        <v>50.51727888624421</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5642603550295858</v>
+        <v>1.488946724116117</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.5689762367657991</v>
+        <v>-0.01644765893185</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>9103</v>
+        <v>8467</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>205.1766051139335</v>
+        <v>219.268740454676</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>4.89</v>
+        <v>88.3</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>35.72715419923125</v>
+        <v>43.85373891870273</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>10.78468733211324</v>
+        <v>8.164827306505119</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.747843347023613</v>
+        <v>0.5642603550295858</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0011041657054405</v>
+        <v>0.5689762366545361</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8092</v>
+        <v>8478</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>189.744798998913</v>
+        <v>209.9385407400133</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>12.2</v>
+        <v>139.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>33.14200981556225</v>
+        <v>41.72880021286133</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>13.80445114791981</v>
+        <v>7.191915246545872</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6354925783079278</v>
+        <v>0.971835475295568</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0385677286640337</v>
+        <v>0.1665280739422141</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8067</v>
+        <v>9103</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>189.2715978683315</v>
+        <v>205.1766051139335</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>11.2</v>
+        <v>4.89</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>39.07435990822877</v>
+        <v>35.72715423216241</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.82845995178118</v>
+        <v>10.7846872745576</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.634702249603839</v>
+        <v>1.747843347023613</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0057317527543617</v>
+        <v>-0.0011041657076659</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>9110</v>
+        <v>8092</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>184.7420615804066</v>
+        <v>189.744798998913</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>2.95</v>
+        <v>12.2</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>52.07788679958211</v>
+        <v>33.1420093525018</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>4.944468688211666</v>
+        <v>13.80445141114138</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.8393358466351167</v>
+        <v>0.6354925783079278</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.08792329744903191</v>
+        <v>-0.0385677285416344</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8044</v>
+        <v>8067</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>172.718309381481</v>
+        <v>189.2715978683315</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>23.65</v>
+        <v>11.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>43.1383430404798</v>
+        <v>39.07436011245568</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>17.11486056394036</v>
+        <v>15.82845996777082</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.8761910728006919</v>
+        <v>1.634702249603839</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1275994190050186</v>
+        <v>-0.0057317530325403</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8222</v>
+        <v>8423</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>156.5238437152441</v>
+        <v>179.0622918319388</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>35.4</v>
+        <v>17.8</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>42.92746368015904</v>
+        <v>44.50762750511853</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>10.25811980634503</v>
+        <v>18.87437655484253</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.256203831583254</v>
+        <v>0.793672779005045</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.139237068709911</v>
+        <v>-0.0142807831763713</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8374</v>
+        <v>8222</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>151.6962883824956</v>
+        <v>176.5238437152441</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>76.90000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>44.73506062383532</v>
+        <v>42.92746353171113</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>8.478540167438609</v>
+        <v>10.25811980901311</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.8427600546756675</v>
+        <v>1.256203831583254</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1260681534666048</v>
+        <v>0.1392370687321581</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>9955</v>
+        <v>8044</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>140.6253996083311</v>
+        <v>172.7183093814811</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>22.9</v>
+        <v>23.65</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>38.11062129912465</v>
+        <v>43.13834309810046</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.5219954910316</v>
+        <v>17.11486062467077</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.047738082084696</v>
+        <v>0.8761910728006919</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.009141856303957</v>
+        <v>0.1275994190495261</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8429</v>
+        <v>8291</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>131.8561983536327</v>
+        <v>152.8503243604718</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>5.9</v>
+        <v>28.1</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.83989023053054</v>
+        <v>38.96083720678972</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>8.011686216706837</v>
+        <v>5.942279895656172</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.8381707202212284</v>
+        <v>0.4967631663826448</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0046559826295872</v>
+        <v>0.0831255484662434</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8478</v>
+        <v>8429</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>99.93854074001339</v>
+        <v>151.8561983536317</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>139.5</v>
+        <v>5.9</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>41.72880085152965</v>
+        <v>42.83989025911323</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7.191915061712732</v>
+        <v>8.01168623950414</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.971835475295568</v>
+        <v>0.8381707202212284</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.166528072273157</v>
+        <v>0.0046559826318119</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8291</v>
+        <v>9955</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>92.85032436047184</v>
+        <v>140.625399608331</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>28.1</v>
+        <v>22.9</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>38.95123235830104</v>
+        <v>38.11062132063558</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>5.941114066901784</v>
+        <v>13.5219955542373</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.4967631663826448</v>
+        <v>1.047738082084696</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.08319208339438371</v>
+        <v>-0.009141856370719299</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
